--- a/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
+++ b/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="1282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7081" uniqueCount="1300">
   <si>
     <t>Item</t>
   </si>
@@ -127,10 +127,10 @@
     <t>QDB foundation refactoring (publisher, qdb_ schema, namespace, platform config/mapping, CRM abstraction, tooling adapters, queue fix, CI/CD)</t>
   </si>
   <si>
-    <t>Complete — at gate</t>
-  </si>
-  <si>
-    <t>qdb_ schema provisioned on org5869857f under publisher qdb (optVal 10000): 12 entities, 243 columns, 17 relationships + Customer lookup, 30 choices, 23 status reasons, 3 keys, 12 roles. 0 failures. Plugins retargeted and registered beside the legacy assembly (4 types, 10 steps). verify-qdb-schema 19/19; smoke-qdb-plugins 13/13; C# 105, TS 120, tooling 10. See docs/phases/Phase_1_Completion_Report.md. Phase 2 not started.</t>
+    <t>Complete — closed out, awaiting Phase 2 approval</t>
+  </si>
+  <si>
+    <t>qdb_ schema provisioned on org5869857f under publisher qdb (optVal 10000): 12 entities, 243 columns, 17 relationships + Customer lookup, 30 choices, 23 status reasons, 3 keys, 12 roles. 0 failures. Plugins retargeted and registered beside the legacy assembly (4 types, 10 steps). verify-qdb-schema 19/19; smoke-qdb-plugins 13/13; C# 105, TS 120, tooling 10. See docs/phases/Phase_1_Completion_Report.md. Phase 2 not started. CLOSE-OUT 2026-09-17: KI-40 fixed on the live msst_ registration (2 steps, registration only, verified live); KI-42/KI-04 sandbox cleaned (7 records, guards restored, zero SMOKE- rows left); KI-45 communication architecture confirmed and closed; KI-43 classified Legacy; KI-44 left as a QDB configuration dependency; KI-12 baseline committed as 4 commits on feat/dcp-phase1-foundation and feat/dcp-phase2-core-model created. See Phase_1_Completion_Report.md §10-§11.</t>
   </si>
   <si>
     <t>Phase 2</t>
@@ -3166,6 +3166,42 @@
     <t>A completed msst_ action or communication is editable column by column (KI-40)</t>
   </si>
   <si>
+    <t>Exact fax fields that distinguish SMS from WhatsApp</t>
+  </si>
+  <si>
+    <t>CommunicationArchitecture §7.1, §9 — the existing QDB workflow reads them</t>
+  </si>
+  <si>
+    <t>Implementation detail of the confirmed model (KI-45); does not block the architecture</t>
+  </si>
+  <si>
+    <t>DCP-origin marker, if regardingobjectid = Collection Case cannot carry attribution</t>
+  </si>
+  <si>
+    <t>CommunicationArchitecture §7.3 — correlate, never duplicate</t>
+  </si>
+  <si>
+    <t>Determines how DCP-originated communications are identified in the unified history</t>
+  </si>
+  <si>
+    <t>Warning Letter physical/document source</t>
+  </si>
+  <si>
+    <t>CommunicationArchitecture §7.1 — the approved QDB document capability</t>
+  </si>
+  <si>
+    <t>Fourth source of the unified Communication History</t>
+  </si>
+  <si>
+    <t>Delivery-status fields reported by the existing QDB fax/email mechanisms</t>
+  </si>
+  <si>
+    <t>CommunicationArchitecture §6, §7.4</t>
+  </si>
+  <si>
+    <t>Absent status renders as unknown; never inferred</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
@@ -3866,6 +3902,24 @@
   </si>
   <si>
     <t>no on-premises organisation for DCP (KI-22)</t>
+  </si>
+  <si>
+    <t>Live verification after cleanup — verify-qdb-schema.mjs</t>
+  </si>
+  <si>
+    <t>guards restored and re-proven after the authorised smoke-data cleanup</t>
+  </si>
+  <si>
+    <t>Live smoke after cleanup — smoke-qdb-plugins.mjs</t>
+  </si>
+  <si>
+    <t>every immutability assertion passed; that run’s own rows were then cleaned</t>
+  </si>
+  <si>
+    <t>Live verification — KI-40 msst_ immutability correction</t>
+  </si>
+  <si>
+    <t>completed activity and communication both refuse an ordinary update; delete still blocked; open records and completion still work</t>
   </si>
 </sst>
 </file>
@@ -4360,7 +4414,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -4371,7 +4425,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1254</v>
+        <v>1266</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>155</v>
@@ -4380,10 +4434,10 @@
         <v>519</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1255</v>
+        <v>1267</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1256</v>
+        <v>1268</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>26</v>
@@ -4391,7 +4445,7 @@
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1257</v>
+        <v>1269</v>
       </c>
       <c r="B2" s="2">
         <v>92</v>
@@ -4406,12 +4460,12 @@
         <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1258</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1259</v>
+        <v>1271</v>
       </c>
       <c r="B3" s="2">
         <v>19</v>
@@ -4426,12 +4480,12 @@
         <v>30</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1260</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1261</v>
+        <v>1273</v>
       </c>
       <c r="B4" s="2">
         <v>14</v>
@@ -4446,12 +4500,12 @@
         <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1263</v>
+        <v>1275</v>
       </c>
       <c r="B5" s="2">
         <v>12</v>
@@ -4471,7 +4525,7 @@
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1264</v>
+        <v>1276</v>
       </c>
       <c r="B6" s="2">
         <v>14</v>
@@ -4486,12 +4540,12 @@
         <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1265</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1266</v>
+        <v>1278</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>40</v>
@@ -4503,15 +4557,15 @@
         <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1268</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1269</v>
+        <v>1281</v>
       </c>
       <c r="B8" s="2">
         <v>105</v>
@@ -4526,12 +4580,12 @@
         <v>31</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1270</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1259</v>
+        <v>1271</v>
       </c>
       <c r="B9" s="2">
         <v>49</v>
@@ -4546,12 +4600,12 @@
         <v>31</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1271</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1272</v>
+        <v>1284</v>
       </c>
       <c r="B10" s="2">
         <v>30</v>
@@ -4566,12 +4620,12 @@
         <v>31</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1273</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1263</v>
+        <v>1275</v>
       </c>
       <c r="B11" s="2">
         <v>27</v>
@@ -4586,12 +4640,12 @@
         <v>31</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1274</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1261</v>
+        <v>1273</v>
       </c>
       <c r="B12" s="2">
         <v>14</v>
@@ -4606,12 +4660,12 @@
         <v>31</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1275</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1276</v>
+        <v>1288</v>
       </c>
       <c r="B13" s="2">
         <v>10</v>
@@ -4626,12 +4680,12 @@
         <v>31</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1275</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1277</v>
+        <v>1289</v>
       </c>
       <c r="B14" s="2">
         <v>19</v>
@@ -4646,12 +4700,12 @@
         <v>31</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1278</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1279</v>
+        <v>1291</v>
       </c>
       <c r="B15" s="2">
         <v>13</v>
@@ -4666,12 +4720,12 @@
         <v>31</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1280</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1266</v>
+        <v>1278</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>40</v>
@@ -4683,10 +4737,70 @@
         <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1281</v>
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B17" s="2">
+        <v>19</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B18" s="2">
+        <v>13</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B19" s="2">
+        <v>4</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>1299</v>
       </c>
     </row>
   </sheetData>
@@ -25819,7 +25933,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -26470,6 +26584,62 @@
       </c>
       <c r="D46" s="2" t="s">
         <v>1047</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>1059</v>
       </c>
     </row>
   </sheetData>
@@ -26493,16 +26663,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1048</v>
+        <v>1060</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1050</v>
+        <v>1062</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1051</v>
+        <v>1063</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>23</v>
@@ -26510,240 +26680,240 @@
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1053</v>
+        <v>1065</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1054</v>
+        <v>1066</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1055</v>
+        <v>1067</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1064</v>
+        <v>1076</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1069</v>
+        <v>1081</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1071</v>
+        <v>1083</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1073</v>
+        <v>1085</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1074</v>
+        <v>1086</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1075</v>
+        <v>1087</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1076</v>
+        <v>1088</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>1077</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1078</v>
+        <v>1090</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1079</v>
+        <v>1091</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1081</v>
+        <v>1093</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1082</v>
+        <v>1094</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1083</v>
+        <v>1095</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1084</v>
+        <v>1096</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1085</v>
+        <v>1097</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1086</v>
+        <v>1098</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1087</v>
+        <v>1099</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1088</v>
+        <v>1100</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1089</v>
+        <v>1101</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1090</v>
+        <v>1102</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1091</v>
+        <v>1103</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1092</v>
+        <v>1104</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1094</v>
+        <v>1106</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1095</v>
+        <v>1107</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1096</v>
+        <v>1108</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1097</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1098</v>
+        <v>1110</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1099</v>
+        <v>1111</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1102</v>
+        <v>1114</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1104</v>
+        <v>1116</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1105</v>
+        <v>1117</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1106</v>
+        <v>1118</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1107</v>
+        <v>1119</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1108</v>
+        <v>1120</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1110</v>
+        <v>1122</v>
       </c>
     </row>
   </sheetData>
@@ -26767,16 +26937,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1111</v>
+        <v>1123</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1112</v>
+        <v>1124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1113</v>
+        <v>1125</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>23</v>
@@ -26784,118 +26954,118 @@
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1116</v>
+        <v>1128</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1117</v>
+        <v>1129</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1118</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1119</v>
+        <v>1131</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1120</v>
+        <v>1132</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1121</v>
+        <v>1133</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1122</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1123</v>
+        <v>1135</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1124</v>
+        <v>1136</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1125</v>
+        <v>1137</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1126</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1127</v>
+        <v>1139</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1128</v>
+        <v>1140</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1129</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1131</v>
+        <v>1143</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1132</v>
+        <v>1144</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1133</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1134</v>
+        <v>1146</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1135</v>
+        <v>1147</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1136</v>
+        <v>1148</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1137</v>
+        <v>1149</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1138</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1139</v>
+        <v>1151</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1141</v>
+        <v>1153</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>895</v>
@@ -26903,16 +27073,16 @@
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1139</v>
+        <v>1151</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1142</v>
+        <v>1154</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1143</v>
+        <v>1155</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1144</v>
+        <v>1156</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>895</v>
@@ -26920,169 +27090,169 @@
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1147</v>
+        <v>1159</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1148</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1149</v>
+        <v>1161</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1150</v>
+        <v>1162</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1148</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1151</v>
+        <v>1163</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1148</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1152</v>
+        <v>1164</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1153</v>
+        <v>1165</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1154</v>
+        <v>1166</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1148</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1155</v>
+        <v>1167</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1153</v>
+        <v>1165</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1156</v>
+        <v>1168</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1148</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1153</v>
+        <v>1165</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1157</v>
+        <v>1169</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1158</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>349</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1153</v>
+        <v>1165</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1159</v>
+        <v>1171</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1160</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1161</v>
+        <v>1173</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1131</v>
+        <v>1143</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1162</v>
+        <v>1174</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1163</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1131</v>
+        <v>1143</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1164</v>
+        <v>1176</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1148</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>1165</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1153</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>1167</v>
+        <v>1179</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>895</v>
@@ -27090,50 +27260,50 @@
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>1168</v>
+        <v>1180</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1169</v>
+        <v>1181</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1170</v>
+        <v>1182</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1171</v>
+        <v>1183</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1172</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1173</v>
+        <v>1185</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1174</v>
+        <v>1186</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1175</v>
+        <v>1187</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1176</v>
+        <v>1188</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1177</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1173</v>
+        <v>1185</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1178</v>
+        <v>1190</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>895</v>
@@ -27141,19 +27311,19 @@
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1181</v>
+        <v>1193</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1183</v>
+        <v>1195</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1184</v>
+        <v>1196</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1185</v>
+        <v>1197</v>
       </c>
     </row>
   </sheetData>
@@ -27178,33 +27348,33 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1186</v>
+        <v>1198</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1189</v>
+        <v>1201</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1190</v>
+        <v>1202</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1191</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1192</v>
+        <v>1204</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1193</v>
+        <v>1205</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1194</v>
+        <v>1206</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>158</v>
@@ -27213,18 +27383,18 @@
         <v>109</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1195</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1196</v>
+        <v>1208</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1197</v>
+        <v>1209</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1198</v>
+        <v>1210</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>158</v>
@@ -27233,35 +27403,35 @@
         <v>109</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1200</v>
+        <v>1212</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1201</v>
+        <v>1213</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1202</v>
+        <v>1214</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>158</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1205</v>
+        <v>1217</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1206</v>
+        <v>1218</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>39</v>
@@ -27273,12 +27443,12 @@
         <v>109</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1207</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1208</v>
+        <v>1220</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>153</v>
@@ -27293,18 +27463,18 @@
         <v>109</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1209</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1211</v>
+        <v>1223</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>101</v>
@@ -27313,35 +27483,35 @@
         <v>109</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1213</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1214</v>
+        <v>1226</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1215</v>
+        <v>1227</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>256</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1218</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1219</v>
+        <v>1231</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>156</v>
@@ -27350,38 +27520,38 @@
         <v>101</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1221</v>
+        <v>1233</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1223</v>
+        <v>1235</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1224</v>
+        <v>1236</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>156</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1225</v>
+        <v>1237</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1226</v>
+        <v>1238</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1227</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1228</v>
+        <v>1240</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1229</v>
+        <v>1241</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>39</v>
@@ -27390,35 +27560,35 @@
         <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1230</v>
+        <v>1242</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1231</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1232</v>
+        <v>1244</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1233</v>
+        <v>1245</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1234</v>
+        <v>1246</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1235</v>
+        <v>1247</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>109</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1236</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1237</v>
+        <v>1249</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>153</v>
@@ -27433,15 +27603,15 @@
         <v>109</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1238</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1239</v>
+        <v>1251</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1240</v>
+        <v>1252</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>39</v>
@@ -27450,50 +27620,50 @@
         <v>39</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1241</v>
+        <v>1253</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1242</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1243</v>
+        <v>1255</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1245</v>
+        <v>1257</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1246</v>
+        <v>1258</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1248</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1249</v>
+        <v>1261</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1250</v>
+        <v>1262</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1251</v>
+        <v>1263</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>158</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1252</v>
+        <v>1264</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1253</v>
+        <v>1265</v>
       </c>
     </row>
   </sheetData>

--- a/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
+++ b/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
@@ -1922,13 +1922,13 @@
         <v>Real React Collection Workspace (full-page web resource)</v>
       </c>
       <c r="C7" t="str">
-        <v>In Progress — local gate green; stopped for interactive Cloud runtime validation</v>
+        <v>Complete — runtime validated inside Dynamics; approved 2026-09-19</v>
       </c>
       <c r="D7" t="str">
         <v>2026-09-18 21:02:36 (+03:00 Asia/Qatar)</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>2026-09-19 13:28:05 (+03:00 Asia/Qatar)</v>
       </c>
       <c r="F7" t="str">
         <v>React Collection Workspace — the APPROVED prototype/ baseline (21 views, 7 pages, role-aware, dual-CRM, Dynamics UCI) converted into one React application deployed as the single-file web resource qdb_dcp_workspace.html. All 21 views present; 13 functional, 8 preserved with their owning phase stated. Large-data engine bounds every list: 100,000 rows, 50 fetched, 16 rendered. Evidence on org5869857f: browser-adapter spike 16/16, query smoke 45/45 (0 residue), column verifier 11/11 across 173 columns, web resource deployed and published 10/10. Phase 1-4 regression 13/13, 20/20, 19/19, 22/22; schema 244/244 unchanged; no CRM schema change. AWAITING INTERACTIVE CLOUD RUNTIME VALIDATION: that the workspace loads inside Dynamics, that getGlobalContext answers, and that it reads as the signed-in user all need an authenticated browser session and are NOT claimed. Estimated 32.50 h, never revised.</v>
@@ -1942,16 +1942,16 @@
         <v>Collection activities &amp; PTP</v>
       </c>
       <c r="C8" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>2026-09-19 13:28:05 (+03:00 Asia/Qatar)</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Not authorised. Phase 5 must be approved first.</v>
+        <v>Collection Activities, Action Plan &amp; Promise-to-Pay. Estimated 36.50 Claude execution hours; expected completion 2026-09-21 01:58:05 (+03:00). Breakdown in docs/evidence/Phase6_timing.md. Branch feat/dcp-phase6-activities-ptp from the approved Phase 5 baseline 76f84ce2. SCOPE REVIEW FINDINGS: (1) the activity statuscode lifecycle has NO server-side validator — StatusTransitionValidatorPlugin filters qdb_ptpstatus only, and the workspace writes directly through Xrm.WebApi, so server-side enforcement means a plugin change and an assembly redeploy; (2) browser writes (create/update/retrieveByKey) are typed and unit-tested but have NEVER made a real call; (3) Xrm.WebApi exposes no If-Match, so Dataverse ETag concurrency is not reachable through the client API and needs a spike before any write screen is built on it; (4) qdb_collectionactivitytype holds 1 row (a DEMO seed) — the eleven approved types are not provisioned; (5) qdb_activityoutcome holds 0 rows, and it carries qdb_requiresfollowup / qdb_followupdays / qdb_requiresnotes / qdb_escalationrequired — so outcome configuration DRIVES Phase 6 behaviour and the catalogue is a QDB confirmation. Does NOT own communications transport (Phase 7), automated strategy execution (Phase 8), workout/legal/deceased (Phase 9) or reporting (Phase 10).</v>
       </c>
     </row>
     <row r="9">

--- a/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
+++ b/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
@@ -1951,7 +1951,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Collection Activities, Action Plan &amp; Promise-to-Pay. Estimated 36.50 Claude execution hours; expected completion 2026-09-21 01:58:05 (+03:00). Breakdown in docs/evidence/Phase6_timing.md. Branch feat/dcp-phase6-activities-ptp from the approved Phase 5 baseline 76f84ce2. SCOPE REVIEW FINDINGS: (1) the activity statuscode lifecycle has NO server-side validator — StatusTransitionValidatorPlugin filters qdb_ptpstatus only, and the workspace writes directly through Xrm.WebApi, so server-side enforcement means a plugin change and an assembly redeploy; (2) browser writes (create/update/retrieveByKey) are typed and unit-tested but have NEVER made a real call; (3) Xrm.WebApi exposes no If-Match, so Dataverse ETag concurrency is not reachable through the client API and needs a spike before any write screen is built on it; (4) qdb_collectionactivitytype holds 1 row (a DEMO seed) — the eleven approved types are not provisioned; (5) qdb_activityoutcome holds 0 rows, and it carries qdb_requiresfollowup / qdb_followupdays / qdb_requiresnotes / qdb_escalationrequired — so outcome configuration DRIVES Phase 6 behaviour and the catalogue is a QDB confirmation. Does NOT own communications transport (Phase 7), automated strategy execution (Phase 8), workout/legal/deceased (Phase 9) or reporting (Phase 10).</v>
+        <v>Collection Activities, Action Plan &amp; Promise-to-Pay. Estimated 36.50 Claude execution hours; expected completion 2026-09-21 01:58:05 (+03:00). Breakdown in docs/evidence/Phase6_timing.md. Branch feat/dcp-phase6-activities-ptp from the approved Phase 5 baseline 76f84ce2. SCOPE REVIEW FINDINGS: (1) the activity statuscode lifecycle has NO server-side validator — StatusTransitionValidatorPlugin filters qdb_ptpstatus only, and the workspace writes directly through Xrm.WebApi, so server-side enforcement means a plugin change and an assembly redeploy; (2) browser writes (create/update/retrieveByKey) are typed and unit-tested but have NEVER made a real call; (3) Xrm.WebApi exposes no If-Match, so Dataverse ETag concurrency is not reachable through the client API and needs a spike before any write screen is built on it; (4) qdb_collectionactivitytype holds 1 row (a DEMO seed) — the eleven approved types are not provisioned; (5) qdb_activityoutcome holds 0 rows, and it carries qdb_requiresfollowup / qdb_followupdays / qdb_requiresnotes / qdb_escalationrequired — so outcome configuration DRIVES Phase 6 behaviour and the catalogue is a QDB confirmation. Does NOT own communications transport (Phase 7), automated strategy execution (Phase 8), workout/legal/deceased (Phase 9) or reporting (Phase 10). PACKAGES 6-8 COMPLETE 2026-09-19: domain operations layer (activityOperations.ts) decides in canonical terms; ActivityService translates a plan to Dataverse columns and bindLookup() navigation properties, so React composes no write. Three distinct save outcomes kept apart — refused / conflict / thrown; the conflict message carries no HTTP or ETag vocabulary. Idempotent create by client-chosen primary key + If-None-Match: * (ADR-DCP-19); a repeat is success, not an error. Query modules added for the follow-up queue (date comparison sent to the platform) and the Action Plan (correlated on the activity type ID, never the editable label). ADR-DCP-18 and ADR-DCP-19 written up in docs/ADR_Phase6_Writes.md and added to the Architecture register — ADR-18 had only ever been referenced. LIVE 41/41 on org5869857f (docs/evidence/Phase6_domain_operations_smoke.txt): activity create/complete with outcome-driven notes and configured follow-up, PTP create/transition, invalid transition refused, stale write refused AND proved not to have overwritten, two consecutive legitimate saves, duplicate submission leaving exactly one row, multi-page paging with zero duplicates, continuation reset, HL contact and BFD account contexts, Action Plan with its negative case. NEW ISSUES: KI-71 (no schema link from an activity to the strategy action that produced it — correspondence, never provenance; resolve before Phase 8), KI-72 (no PTP policy limits in evidence — none invented, absences asserted by test), KI-73 CLOSED (the smoke cleaner reported success while leaving six rows; markerField now accepts several columns, accounts and activity outcomes added, re-proved 13 removed / 0 residue / guards restored). KI-65 remains open. 931 TS tests, type-check clean. Estimate unrevised at 36.50h. NEXT: Phase 6 UI packages 9-13. Phase 7 NOT started.</v>
       </c>
     </row>
     <row r="9">

--- a/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
+++ b/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
@@ -1951,7 +1951,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Collection Activities, Action Plan &amp; Promise-to-Pay. Estimated 36.50 Claude execution hours; expected completion 2026-09-21 01:58:05 (+03:00). Breakdown in docs/evidence/Phase6_timing.md. Branch feat/dcp-phase6-activities-ptp from the approved Phase 5 baseline 76f84ce2. SCOPE REVIEW FINDINGS: (1) the activity statuscode lifecycle has NO server-side validator — StatusTransitionValidatorPlugin filters qdb_ptpstatus only, and the workspace writes directly through Xrm.WebApi, so server-side enforcement means a plugin change and an assembly redeploy; (2) browser writes (create/update/retrieveByKey) are typed and unit-tested but have NEVER made a real call; (3) Xrm.WebApi exposes no If-Match, so Dataverse ETag concurrency is not reachable through the client API and needs a spike before any write screen is built on it; (4) qdb_collectionactivitytype holds 1 row (a DEMO seed) — the eleven approved types are not provisioned; (5) qdb_activityoutcome holds 0 rows, and it carries qdb_requiresfollowup / qdb_followupdays / qdb_requiresnotes / qdb_escalationrequired — so outcome configuration DRIVES Phase 6 behaviour and the catalogue is a QDB confirmation. Does NOT own communications transport (Phase 7), automated strategy execution (Phase 8), workout/legal/deceased (Phase 9) or reporting (Phase 10). PACKAGES 6-8 COMPLETE 2026-09-19: domain operations layer (activityOperations.ts) decides in canonical terms; ActivityService translates a plan to Dataverse columns and bindLookup() navigation properties, so React composes no write. Three distinct save outcomes kept apart — refused / conflict / thrown; the conflict message carries no HTTP or ETag vocabulary. Idempotent create by client-chosen primary key + If-None-Match: * (ADR-DCP-19); a repeat is success, not an error. Query modules added for the follow-up queue (date comparison sent to the platform) and the Action Plan (correlated on the activity type ID, never the editable label). ADR-DCP-18 and ADR-DCP-19 written up in docs/ADR_Phase6_Writes.md and added to the Architecture register — ADR-18 had only ever been referenced. LIVE 41/41 on org5869857f (docs/evidence/Phase6_domain_operations_smoke.txt): activity create/complete with outcome-driven notes and configured follow-up, PTP create/transition, invalid transition refused, stale write refused AND proved not to have overwritten, two consecutive legitimate saves, duplicate submission leaving exactly one row, multi-page paging with zero duplicates, continuation reset, HL contact and BFD account contexts, Action Plan with its negative case. NEW ISSUES: KI-71 (no schema link from an activity to the strategy action that produced it — correspondence, never provenance; resolve before Phase 8), KI-72 (no PTP policy limits in evidence — none invented, absences asserted by test), KI-73 CLOSED (the smoke cleaner reported success while leaving six rows; markerField now accepts several columns, accounts and activity outcomes added, re-proved 13 removed / 0 residue / guards restored). KI-65 remains open. 931 TS tests, type-check clean. Estimate unrevised at 36.50h. NEXT: Phase 6 UI packages 9-13. Phase 7 NOT started.</v>
+        <v>Collection Activities, Action Plan &amp; Promise-to-Pay. Estimated 36.50 Claude execution hours; expected completion 2026-09-21 01:58:05 (+03:00). Breakdown in docs/evidence/Phase6_timing.md. Branch feat/dcp-phase6-activities-ptp from the approved Phase 5 baseline 76f84ce2. SCOPE REVIEW FINDINGS: (1) the activity statuscode lifecycle has NO server-side validator — StatusTransitionValidatorPlugin filters qdb_ptpstatus only, and the workspace writes directly through Xrm.WebApi, so server-side enforcement means a plugin change and an assembly redeploy; (2) browser writes (create/update/retrieveByKey) are typed and unit-tested but have NEVER made a real call; (3) Xrm.WebApi exposes no If-Match, so Dataverse ETag concurrency is not reachable through the client API and needs a spike before any write screen is built on it; (4) qdb_collectionactivitytype holds 1 row (a DEMO seed) — the eleven approved types are not provisioned; (5) qdb_activityoutcome holds 0 rows, and it carries qdb_requiresfollowup / qdb_followupdays / qdb_requiresnotes / qdb_escalationrequired — so outcome configuration DRIVES Phase 6 behaviour and the catalogue is a QDB confirmation. Does NOT own communications transport (Phase 7), automated strategy execution (Phase 8), workout/legal/deceased (Phase 9) or reporting (Phase 10). PACKAGES 6-8 COMPLETE 2026-09-19: domain operations layer (activityOperations.ts) decides in canonical terms; ActivityService translates a plan to Dataverse columns and bindLookup() navigation properties, so React composes no write. Three distinct save outcomes kept apart — refused / conflict / thrown; the conflict message carries no HTTP or ETag vocabulary. Idempotent create by client-chosen primary key + If-None-Match: * (ADR-DCP-19); a repeat is success, not an error. Query modules added for the follow-up queue (date comparison sent to the platform) and the Action Plan (correlated on the activity type ID, never the editable label). ADR-DCP-18 and ADR-DCP-19 written up in docs/ADR_Phase6_Writes.md and added to the Architecture register — ADR-18 had only ever been referenced. LIVE 41/41 on org5869857f (docs/evidence/Phase6_domain_operations_smoke.txt): activity create/complete with outcome-driven notes and configured follow-up, PTP create/transition, invalid transition refused, stale write refused AND proved not to have overwritten, two consecutive legitimate saves, duplicate submission leaving exactly one row, multi-page paging with zero duplicates, continuation reset, HL contact and BFD account contexts, Action Plan with its negative case. NEW ISSUES: KI-71 (no schema link from an activity to the strategy action that produced it — correspondence, never provenance; resolve before Phase 8), KI-72 (no PTP policy limits in evidence — none invented, absences asserted by test), KI-73 CLOSED (the smoke cleaner reported success while leaving six rows; markerField now accepts several columns, accounts and activity outcomes added, re-proved 13 removed / 0 residue / guards restored). KI-65 remains open. 931 TS tests, type-check clean. Estimate unrevised at 36.50h. NEXT: Phase 6 UI packages 9-13. Phase 7 NOT started. PACKAGES 9-13 COMPLETE 2026-09-19 (UI): ActivityDialog and PromiseDialog log, edit, complete, cancel and transition from Case &gt; Actions and Case &gt; PTP; activity type and outcome come from configuration and outcomes are filtered to the chosen type; a retired row renders on the record using it but is not selectable for a new one. Outcome configuration (requiresnotes / requiresfollowup / followupdays / escalationrequired) is reflected before save; escalation is DISPLAYED as configuration and not acted on (Phase 8). PTP stays qdb_collectionactivity with a PTP type — no parallel model, no policy limits (KI-72) — and a recorded outcome is marked unverified in every grid and in the form, because nothing can assert payment (KI-53). Conflict UX: refused / conflict / failed stay distinct to the screen; a conflict offers Reload latest only, never save-anyway or silent merge; no 412/ETag/If-Match/RowVersion reaches an officer (asserted by scanning the rendered document). Save disables in flight via a ref (two clicks in one tick read the same rendered prop); ADR-DCP-19 remains the real duplicate protection and the dialog mints the id once on open. My Day gains an operational follow-up queue with a SERVER-SIDE window filter and a pinned now; no second follow-up entity. Action Plan correlates by activity type ID and states on screen that this is correspondence, not provenance (KI-71 stays open). Zero new layout — the prototype had already designed forms; phase6.css adds four rules, all existing tokens. styleContract.test.ts STRENGTHENED to read class names out of ternaries (previously unchecked) and verified by reintroducing an unstyled class. NEW: KI-74 CLOSED — the Phase 6 configuration had been seeded unusable (11 types all inactive, 7 outcomes with no owning type; green tests, empty dropdowns); seeder now writes isactive/sequence explicitly, seeds outcomes per type via the metadata-verified navigation property qdb_activitytypeid, and re-reads to assert zero orphans. LIVE on org5869857f: smoke-domain-operations 50/50, verify-view-columns 17/17 across 205 names, deploy+publish 11/11 byte-for-byte; 11 active types and 30 owned outcomes seeded. 960 TS tests (360 domain, 241 web), type-check clean. Estimate unrevised at 36.50h. ▶ NEXT: MANUAL RUNTIME VALIDATION BY THE USER inside main.aspx?pagetype=webresource&amp;webresourceName=qdb_dcp_workspace.html — NOT claimed by the build. Phase 7 NOT started.</v>
       </c>
     </row>
     <row r="9">

--- a/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
+++ b/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
@@ -1942,16 +1942,16 @@
         <v>Collection activities &amp; PTP</v>
       </c>
       <c r="C8" t="str">
-        <v>In Progress</v>
+        <v>Complete — runtime validated inside Dynamics by the client; approved 2026-09-19</v>
       </c>
       <c r="D8" t="str">
         <v>2026-09-19 13:28:05 (+03:00 Asia/Qatar)</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>2026-09-19 21:05 (+03:00 Asia/Qatar)</v>
       </c>
       <c r="F8" t="str">
-        <v>Collection Activities, Action Plan &amp; Promise-to-Pay. Estimated 36.50 Claude execution hours; expected completion 2026-09-21 01:58:05 (+03:00). Breakdown in docs/evidence/Phase6_timing.md. Branch feat/dcp-phase6-activities-ptp from the approved Phase 5 baseline 76f84ce2. SCOPE REVIEW FINDINGS: (1) the activity statuscode lifecycle has NO server-side validator — StatusTransitionValidatorPlugin filters qdb_ptpstatus only, and the workspace writes directly through Xrm.WebApi, so server-side enforcement means a plugin change and an assembly redeploy; (2) browser writes (create/update/retrieveByKey) are typed and unit-tested but have NEVER made a real call; (3) Xrm.WebApi exposes no If-Match, so Dataverse ETag concurrency is not reachable through the client API and needs a spike before any write screen is built on it; (4) qdb_collectionactivitytype holds 1 row (a DEMO seed) — the eleven approved types are not provisioned; (5) qdb_activityoutcome holds 0 rows, and it carries qdb_requiresfollowup / qdb_followupdays / qdb_requiresnotes / qdb_escalationrequired — so outcome configuration DRIVES Phase 6 behaviour and the catalogue is a QDB confirmation. Does NOT own communications transport (Phase 7), automated strategy execution (Phase 8), workout/legal/deceased (Phase 9) or reporting (Phase 10). PACKAGES 6-8 COMPLETE 2026-09-19: domain operations layer (activityOperations.ts) decides in canonical terms; ActivityService translates a plan to Dataverse columns and bindLookup() navigation properties, so React composes no write. Three distinct save outcomes kept apart — refused / conflict / thrown; the conflict message carries no HTTP or ETag vocabulary. Idempotent create by client-chosen primary key + If-None-Match: * (ADR-DCP-19); a repeat is success, not an error. Query modules added for the follow-up queue (date comparison sent to the platform) and the Action Plan (correlated on the activity type ID, never the editable label). ADR-DCP-18 and ADR-DCP-19 written up in docs/ADR_Phase6_Writes.md and added to the Architecture register — ADR-18 had only ever been referenced. LIVE 41/41 on org5869857f (docs/evidence/Phase6_domain_operations_smoke.txt): activity create/complete with outcome-driven notes and configured follow-up, PTP create/transition, invalid transition refused, stale write refused AND proved not to have overwritten, two consecutive legitimate saves, duplicate submission leaving exactly one row, multi-page paging with zero duplicates, continuation reset, HL contact and BFD account contexts, Action Plan with its negative case. NEW ISSUES: KI-71 (no schema link from an activity to the strategy action that produced it — correspondence, never provenance; resolve before Phase 8), KI-72 (no PTP policy limits in evidence — none invented, absences asserted by test), KI-73 CLOSED (the smoke cleaner reported success while leaving six rows; markerField now accepts several columns, accounts and activity outcomes added, re-proved 13 removed / 0 residue / guards restored). KI-65 remains open. 931 TS tests, type-check clean. Estimate unrevised at 36.50h. NEXT: Phase 6 UI packages 9-13. Phase 7 NOT started. PACKAGES 9-13 COMPLETE 2026-09-19 (UI): ActivityDialog and PromiseDialog log, edit, complete, cancel and transition from Case &gt; Actions and Case &gt; PTP; activity type and outcome come from configuration and outcomes are filtered to the chosen type; a retired row renders on the record using it but is not selectable for a new one. Outcome configuration (requiresnotes / requiresfollowup / followupdays / escalationrequired) is reflected before save; escalation is DISPLAYED as configuration and not acted on (Phase 8). PTP stays qdb_collectionactivity with a PTP type — no parallel model, no policy limits (KI-72) — and a recorded outcome is marked unverified in every grid and in the form, because nothing can assert payment (KI-53). Conflict UX: refused / conflict / failed stay distinct to the screen; a conflict offers Reload latest only, never save-anyway or silent merge; no 412/ETag/If-Match/RowVersion reaches an officer (asserted by scanning the rendered document). Save disables in flight via a ref (two clicks in one tick read the same rendered prop); ADR-DCP-19 remains the real duplicate protection and the dialog mints the id once on open. My Day gains an operational follow-up queue with a SERVER-SIDE window filter and a pinned now; no second follow-up entity. Action Plan correlates by activity type ID and states on screen that this is correspondence, not provenance (KI-71 stays open). Zero new layout — the prototype had already designed forms; phase6.css adds four rules, all existing tokens. styleContract.test.ts STRENGTHENED to read class names out of ternaries (previously unchecked) and verified by reintroducing an unstyled class. NEW: KI-74 CLOSED — the Phase 6 configuration had been seeded unusable (11 types all inactive, 7 outcomes with no owning type; green tests, empty dropdowns); seeder now writes isactive/sequence explicitly, seeds outcomes per type via the metadata-verified navigation property qdb_activitytypeid, and re-reads to assert zero orphans. LIVE on org5869857f: smoke-domain-operations 50/50, verify-view-columns 17/17 across 205 names, deploy+publish 11/11 byte-for-byte; 11 active types and 30 owned outcomes seeded. 960 TS tests (360 domain, 241 web), type-check clean. Estimate unrevised at 36.50h. ▶ NEXT: MANUAL RUNTIME VALIDATION BY THE USER inside main.aspx?pagetype=webresource&amp;webresourceName=qdb_dcp_workspace.html — NOT claimed by the build. Phase 7 NOT started.</v>
+        <v>Collection Activities, Action Plan &amp; Promise-to-Pay. Estimated 36.50 Claude execution hours; expected completion 2026-09-21 01:58:05 (+03:00). Breakdown in docs/evidence/Phase6_timing.md. Branch feat/dcp-phase6-activities-ptp from the approved Phase 5 baseline 76f84ce2. SCOPE REVIEW FINDINGS: (1) the activity statuscode lifecycle has NO server-side validator — StatusTransitionValidatorPlugin filters qdb_ptpstatus only, and the workspace writes directly through Xrm.WebApi, so server-side enforcement means a plugin change and an assembly redeploy; (2) browser writes (create/update/retrieveByKey) are typed and unit-tested but have NEVER made a real call; (3) Xrm.WebApi exposes no If-Match, so Dataverse ETag concurrency is not reachable through the client API and needs a spike before any write screen is built on it; (4) qdb_collectionactivitytype holds 1 row (a DEMO seed) — the eleven approved types are not provisioned; (5) qdb_activityoutcome holds 0 rows, and it carries qdb_requiresfollowup / qdb_followupdays / qdb_requiresnotes / qdb_escalationrequired — so outcome configuration DRIVES Phase 6 behaviour and the catalogue is a QDB confirmation. Does NOT own communications transport (Phase 7), automated strategy execution (Phase 8), workout/legal/deceased (Phase 9) or reporting (Phase 10). PACKAGES 6-8 COMPLETE 2026-09-19: domain operations layer (activityOperations.ts) decides in canonical terms; ActivityService translates a plan to Dataverse columns and bindLookup() navigation properties, so React composes no write. Three distinct save outcomes kept apart — refused / conflict / thrown; the conflict message carries no HTTP or ETag vocabulary. Idempotent create by client-chosen primary key + If-None-Match: * (ADR-DCP-19); a repeat is success, not an error. Query modules added for the follow-up queue (date comparison sent to the platform) and the Action Plan (correlated on the activity type ID, never the editable label). ADR-DCP-18 and ADR-DCP-19 written up in docs/ADR_Phase6_Writes.md and added to the Architecture register — ADR-18 had only ever been referenced. LIVE 41/41 on org5869857f (docs/evidence/Phase6_domain_operations_smoke.txt): activity create/complete with outcome-driven notes and configured follow-up, PTP create/transition, invalid transition refused, stale write refused AND proved not to have overwritten, two consecutive legitimate saves, duplicate submission leaving exactly one row, multi-page paging with zero duplicates, continuation reset, HL contact and BFD account contexts, Action Plan with its negative case. NEW ISSUES: KI-71 (no schema link from an activity to the strategy action that produced it — correspondence, never provenance; resolve before Phase 8), KI-72 (no PTP policy limits in evidence — none invented, absences asserted by test), KI-73 CLOSED (the smoke cleaner reported success while leaving six rows; markerField now accepts several columns, accounts and activity outcomes added, re-proved 13 removed / 0 residue / guards restored). KI-65 remains open. 931 TS tests, type-check clean. Estimate unrevised at 36.50h. NEXT: Phase 6 UI packages 9-13. Phase 7 NOT started. PACKAGES 9-13 COMPLETE 2026-09-19 (UI): ActivityDialog and PromiseDialog log, edit, complete, cancel and transition from Case &gt; Actions and Case &gt; PTP; activity type and outcome come from configuration and outcomes are filtered to the chosen type; a retired row renders on the record using it but is not selectable for a new one. Outcome configuration (requiresnotes / requiresfollowup / followupdays / escalationrequired) is reflected before save; escalation is DISPLAYED as configuration and not acted on (Phase 8). PTP stays qdb_collectionactivity with a PTP type — no parallel model, no policy limits (KI-72) — and a recorded outcome is marked unverified in every grid and in the form, because nothing can assert payment (KI-53). Conflict UX: refused / conflict / failed stay distinct to the screen; a conflict offers Reload latest only, never save-anyway or silent merge; no 412/ETag/If-Match/RowVersion reaches an officer (asserted by scanning the rendered document). Save disables in flight via a ref (two clicks in one tick read the same rendered prop); ADR-DCP-19 remains the real duplicate protection and the dialog mints the id once on open. My Day gains an operational follow-up queue with a SERVER-SIDE window filter and a pinned now; no second follow-up entity. Action Plan correlates by activity type ID and states on screen that this is correspondence, not provenance (KI-71 stays open). Zero new layout — the prototype had already designed forms; phase6.css adds four rules, all existing tokens. styleContract.test.ts STRENGTHENED to read class names out of ternaries (previously unchecked) and verified by reintroducing an unstyled class. NEW: KI-74 CLOSED — the Phase 6 configuration had been seeded unusable (11 types all inactive, 7 outcomes with no owning type; green tests, empty dropdowns); seeder now writes isactive/sequence explicitly, seeds outcomes per type via the metadata-verified navigation property qdb_activitytypeid, and re-reads to assert zero orphans. LIVE on org5869857f: smoke-domain-operations 50/50, verify-view-columns 17/17 across 205 names, deploy+publish 11/11 byte-for-byte; 11 active types and 30 owned outcomes seeded. 960 TS tests (360 domain, 241 web), type-check clean. Estimate unrevised at 36.50h. ▶ NEXT: MANUAL RUNTIME VALIDATION BY THE USER inside main.aspx?pagetype=webresource&amp;webresourceName=qdb_dcp_workspace.html — NOT claimed by the build. Phase 7 NOT started. PHASE 6 CLOSED 2026-09-19. MANUAL RUNTIME GATE PASSED BY THE CLIENT inside main.aspx on org5869857f across all 12 steps (1, 2, 3a, 3b, 3b-ii, 3b-iii, 4, 5, 6, 7, 8, 9) — the build did NOT award itself this result. Closes KI-56 (workspace had never run inside Dynamics) and KI-67 (concurrency proven from node, not from a browser session cookie; step 7 exercised a real two-window conflict on the cookie). FULL PHASE 1-6 REGRESSION GATE: verify-qdb-schema 19/19, smoke-qdb-plugins 13/13, phase2 20/20, phase3 19/19, phase4 22/22, phase5 45/45, verify-view-columns 17/17 (205 names), verify-activity-lifecycle 9/9, smoke-browser-writes 27/27, smoke-domain-operations 58/58 = 249/249 live checks. 1,133 automated tests (373 domain, 254 web, 313 api, 32 dataverse-client, 14 auth-adapters, 147 C#), type-check clean. Zero SMOKE- residue across 7 tables; preserved 5 DEMO- cases, 4,358 ARR- cases, 11 P6- types, 30 P6- outcomes. Deploy+publish 11/11 byte-for-byte. TWO DEFECTS FOUND ONLY BY RUNNING THE SOFTWARE: KI-75 (adapter built with no write transport — every write and versioned read dead, all tests green) and KI-77 (configured follow-up derived invisibly; the adjacent Save button reported success without recording an outcome). Both now have guards that fail on the real failure. OPEN, none blocking: KI-65, KI-66, KI-71 (resolve before Phase 8), KI-72, KI-76 (collector override of a configured follow-up — QDB confirmation). TIMING: estimate 36.50h; start 2026-09-19 13:28:05 (+03:00), end 21:05 (+03:00); elapsed ~7h37m; blocked ~1h15m (3 rounds of client validation, estimated from commit gaps); effective ~6h20m; variance ~30.2h under (~83%). THE VARIANCE IS AN ESTIMATING ERROR, NOT A PRODUCTIVITY RESULT — do not set the Phase 7 baseline from it without adjustment. On-prem: Compatible by Design — Runtime Test Pending. PHASE 7 NOT STARTED — awaiting client approval.</v>
       </c>
     </row>
     <row r="9">

--- a/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
+++ b/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
@@ -1962,16 +1962,16 @@
         <v>Communication Center</v>
       </c>
       <c r="C9" t="str">
-        <v>Not Started</v>
+        <v>In Progress — discovery complete, awaiting QDB confirmations before build</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>2026-09-19 21:53:42 (+03:00 Asia/Qatar)</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>Communications &amp; Warning Letters. Estimated 13.00 AI-assisted effective execution hours; expected completion 2026-09-20 10:53 (+03:00) on effective hours. Branch feat/dcp-phase7-communications from the accepted Phase 6 baseline 7ebf1381. DISCOVERY COMPLETE 2026-09-19, NO CODE WRITTEN — docs/Phase7_CommunicationContract.md. FINDINGS: (1) fax carries a REAL, coherent QDB SMS schema (31 qdb_ columns: qdb_message_body, qdb_sms_id, qdb_sender QDB|NFG, qdb_sendernumber +97444300000, qdb_smssendto Customer|Prospect|Lead|Customer Contact, qdb_language, qdb_otp, qdb_whatsapptemplate, plus cifno/contact/lead/prospect recipient lookups) — but 0 rows, 0 workflows on fax, and the ONLY plugin step is Microsoft own LeadManagement.SendFax on the Send message. A sweep of 400 workflows and 200 assemblies found every SMS-related item to be Microsoft (Omnichannel/Field Service/Sales Insights). QDB dispatch is NOT INSTALLED here (KI-83). (2) WhatsApp discriminator cannot be established — qdb_whatsapptemplate is plausible but unconfirmed with zero rows (KI-78). (3) Email is standard Dynamics, 0 rows, no DCP-relevant customisation; qdb_reports on email points at the training/trade report entity, NOT letters. (4) qdb_communicationtemplate is fully provisioned with the DCP schema incl. qdb_externaltemplateref — 0 rows. (5) CONTACT HOLD SOURCE DOES NOT EXIST: qdb_stopcontact/qdb_deceasedflag/qdb_dateofdeath/qdb_specialhandling are absent from contact and account; qdb_contactholdrulesetcode is null on both platform configurations; deceased facts live on the SNAPSHOT (qdb_isdeceasedperqcb = the 724 imported flags, MIS data only). Gate therefore FAILS CLOSED (KI-79) — BLOCKS ALL SENDS until QDB nominates the source. (6) Report Engine IS installed (qdb_reportdefinition/layout/version/exportsetting/executionlog) but its 13 definitions are all samples/demos and no SSRS report matches letter/warning/notice/demand/collection — warning-letter mechanism undecided, isolated so it blocks nothing else (KI-81). (7) qdb_privsendsms exists among a family of qdb_priv_* marker entities — QDB authorisation convention, to be checked rather than reinvented (KI-82). (8) qdb_communication ALREADY EXISTS as a Partner Bank activity (qdb_message + qdb_partnerbank) — not created, and deliberately NOT repurposed. NEW: KI-78..KI-83. STATUS LANGUAGE FOR THIS PHASE: Record Creation Proven — Delivery Unproven on this organisation. AWAITING CLIENT DECISION on KI-79 and KI-83 before implementation begins.</v>
       </c>
     </row>
     <row r="10">

--- a/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
+++ b/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Communications &amp; Warning Letters. Estimated 13.00 AI-assisted effective execution hours; expected completion 2026-09-20 10:53 (+03:00) on effective hours. Branch feat/dcp-phase7-communications from the accepted Phase 6 baseline 7ebf1381. DISCOVERY COMPLETE 2026-09-19, NO CODE WRITTEN — docs/Phase7_CommunicationContract.md. FINDINGS: (1) fax carries a REAL, coherent QDB SMS schema (31 qdb_ columns: qdb_message_body, qdb_sms_id, qdb_sender QDB|NFG, qdb_sendernumber +97444300000, qdb_smssendto Customer|Prospect|Lead|Customer Contact, qdb_language, qdb_otp, qdb_whatsapptemplate, plus cifno/contact/lead/prospect recipient lookups) — but 0 rows, 0 workflows on fax, and the ONLY plugin step is Microsoft own LeadManagement.SendFax on the Send message. A sweep of 400 workflows and 200 assemblies found every SMS-related item to be Microsoft (Omnichannel/Field Service/Sales Insights). QDB dispatch is NOT INSTALLED here (KI-83). (2) WhatsApp discriminator cannot be established — qdb_whatsapptemplate is plausible but unconfirmed with zero rows (KI-78). (3) Email is standard Dynamics, 0 rows, no DCP-relevant customisation; qdb_reports on email points at the training/trade report entity, NOT letters. (4) qdb_communicationtemplate is fully provisioned with the DCP schema incl. qdb_externaltemplateref — 0 rows. (5) CONTACT HOLD SOURCE DOES NOT EXIST: qdb_stopcontact/qdb_deceasedflag/qdb_dateofdeath/qdb_specialhandling are absent from contact and account; qdb_contactholdrulesetcode is null on both platform configurations; deceased facts live on the SNAPSHOT (qdb_isdeceasedperqcb = the 724 imported flags, MIS data only). Gate therefore FAILS CLOSED (KI-79) — BLOCKS ALL SENDS until QDB nominates the source. (6) Report Engine IS installed (qdb_reportdefinition/layout/version/exportsetting/executionlog) but its 13 definitions are all samples/demos and no SSRS report matches letter/warning/notice/demand/collection — warning-letter mechanism undecided, isolated so it blocks nothing else (KI-81). (7) qdb_privsendsms exists among a family of qdb_priv_* marker entities — QDB authorisation convention, to be checked rather than reinvented (KI-82). (8) qdb_communication ALREADY EXISTS as a Partner Bank activity (qdb_message + qdb_partnerbank) — not created, and deliberately NOT repurposed. NEW: KI-78..KI-83. STATUS LANGUAGE FOR THIS PHASE: Record Creation Proven — Delivery Unproven on this organisation. AWAITING CLIENT DECISION on KI-79 and KI-83 before implementation begins.</v>
+        <v>Communications &amp; Warning Letters. Estimated 13.00 AI-assisted effective execution hours; expected completion = start + 13.00 EFFECTIVE execution hours (a working-time figure, not a wall-clock date — the span since the recorded start includes a long idle gap that is not execution time; discovery itself was ~30 minutes of tool work). Wall clock at discovery close: 2026-09-20 07:44 (+03:00). Branch feat/dcp-phase7-communications from the accepted Phase 6 baseline 7ebf1381. DISCOVERY COMPLETE 2026-09-19, NO CODE WRITTEN — docs/Phase7_CommunicationContract.md. FINDINGS: (1) fax carries a REAL, coherent QDB SMS schema (31 qdb_ columns: qdb_message_body, qdb_sms_id, qdb_sender QDB|NFG, qdb_sendernumber +97444300000, qdb_smssendto Customer|Prospect|Lead|Customer Contact, qdb_language, qdb_otp, qdb_whatsapptemplate, plus cifno/contact/lead/prospect recipient lookups) — but 0 rows, 0 workflows on fax, and the ONLY plugin step is Microsoft own LeadManagement.SendFax on the Send message. A sweep of 400 workflows and 200 assemblies found every SMS-related item to be Microsoft (Omnichannel/Field Service/Sales Insights). QDB dispatch is NOT INSTALLED here (KI-83). (2) WhatsApp discriminator cannot be established — qdb_whatsapptemplate is plausible but unconfirmed with zero rows (KI-78). (3) Email is standard Dynamics, 0 rows, no DCP-relevant customisation; qdb_reports on email points at the training/trade report entity, NOT letters. (4) qdb_communicationtemplate is fully provisioned with the DCP schema incl. qdb_externaltemplateref — 0 rows. (5) CONTACT HOLD SOURCE DOES NOT EXIST: qdb_stopcontact/qdb_deceasedflag/qdb_dateofdeath/qdb_specialhandling are absent from contact and account; qdb_contactholdrulesetcode is null on both platform configurations; deceased facts live on the SNAPSHOT (qdb_isdeceasedperqcb = the 724 imported flags, MIS data only). Gate therefore FAILS CLOSED (KI-79) — BLOCKS ALL SENDS until QDB nominates the source. (6) Report Engine IS installed (qdb_reportdefinition/layout/version/exportsetting/executionlog) but its 13 definitions are all samples/demos and no SSRS report matches letter/warning/notice/demand/collection — warning-letter mechanism undecided, isolated so it blocks nothing else (KI-81). (7) qdb_privsendsms exists among a family of qdb_priv_* marker entities — QDB authorisation convention, to be checked rather than reinvented (KI-82). (8) qdb_communication ALREADY EXISTS as a Partner Bank activity (qdb_message + qdb_partnerbank) — not created, and deliberately NOT repurposed. NEW: KI-78..KI-83. STATUS LANGUAGE FOR THIS PHASE: Record Creation Proven — Delivery Unproven on this organisation. AWAITING CLIENT DECISION on KI-79 and KI-83 before implementation begins.</v>
       </c>
     </row>
     <row r="10">

--- a/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
+++ b/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
@@ -1962,7 +1962,7 @@
         <v>Communication Center</v>
       </c>
       <c r="C9" t="str">
-        <v>In Progress — discovery complete, awaiting QDB confirmations before build</v>
+        <v>In Progress — implementation baseline approved; single-channel unblocked, bulk resumability awaiting KI-84 schema approval</v>
       </c>
       <c r="D9" t="str">
         <v>2026-09-19 21:53:42 (+03:00 Asia/Qatar)</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Communications &amp; Warning Letters. Estimated 13.00 AI-assisted effective execution hours; expected completion = start + 13.00 EFFECTIVE execution hours (a working-time figure, not a wall-clock date — the span since the recorded start includes a long idle gap that is not execution time; discovery itself was ~30 minutes of tool work). Wall clock at discovery close: 2026-09-20 07:44 (+03:00). Branch feat/dcp-phase7-communications from the accepted Phase 6 baseline 7ebf1381. DISCOVERY COMPLETE 2026-09-19, NO CODE WRITTEN — docs/Phase7_CommunicationContract.md. FINDINGS: (1) fax carries a REAL, coherent QDB SMS schema (31 qdb_ columns: qdb_message_body, qdb_sms_id, qdb_sender QDB|NFG, qdb_sendernumber +97444300000, qdb_smssendto Customer|Prospect|Lead|Customer Contact, qdb_language, qdb_otp, qdb_whatsapptemplate, plus cifno/contact/lead/prospect recipient lookups) — but 0 rows, 0 workflows on fax, and the ONLY plugin step is Microsoft own LeadManagement.SendFax on the Send message. A sweep of 400 workflows and 200 assemblies found every SMS-related item to be Microsoft (Omnichannel/Field Service/Sales Insights). QDB dispatch is NOT INSTALLED here (KI-83). (2) WhatsApp discriminator cannot be established — qdb_whatsapptemplate is plausible but unconfirmed with zero rows (KI-78). (3) Email is standard Dynamics, 0 rows, no DCP-relevant customisation; qdb_reports on email points at the training/trade report entity, NOT letters. (4) qdb_communicationtemplate is fully provisioned with the DCP schema incl. qdb_externaltemplateref — 0 rows. (5) CONTACT HOLD SOURCE DOES NOT EXIST: qdb_stopcontact/qdb_deceasedflag/qdb_dateofdeath/qdb_specialhandling are absent from contact and account; qdb_contactholdrulesetcode is null on both platform configurations; deceased facts live on the SNAPSHOT (qdb_isdeceasedperqcb = the 724 imported flags, MIS data only). Gate therefore FAILS CLOSED (KI-79) — BLOCKS ALL SENDS until QDB nominates the source. (6) Report Engine IS installed (qdb_reportdefinition/layout/version/exportsetting/executionlog) but its 13 definitions are all samples/demos and no SSRS report matches letter/warning/notice/demand/collection — warning-letter mechanism undecided, isolated so it blocks nothing else (KI-81). (7) qdb_privsendsms exists among a family of qdb_priv_* marker entities — QDB authorisation convention, to be checked rather than reinvented (KI-82). (8) qdb_communication ALREADY EXISTS as a Partner Bank activity (qdb_message + qdb_partnerbank) — not created, and deliberately NOT repurposed. NEW: KI-78..KI-83. STATUS LANGUAGE FOR THIS PHASE: Record Creation Proven — Delivery Unproven on this organisation. AWAITING CLIENT DECISION on KI-79 and KI-83 before implementation begins.</v>
+        <v>Communications &amp; Warning Letters. Estimated 13.00 AI-assisted effective execution hours; expected completion = start + 13.00 EFFECTIVE execution hours (a working-time figure, not a wall-clock date — the span since the recorded start includes a long idle gap that is not execution time; discovery itself was ~30 minutes of tool work). Wall clock at discovery close: 2026-09-20 07:44 (+03:00). Branch feat/dcp-phase7-communications from the accepted Phase 6 baseline 7ebf1381. DISCOVERY COMPLETE 2026-09-19, NO CODE WRITTEN — docs/Phase7_CommunicationContract.md. FINDINGS: (1) fax carries a REAL, coherent QDB SMS schema (31 qdb_ columns: qdb_message_body, qdb_sms_id, qdb_sender QDB|NFG, qdb_sendernumber +97444300000, qdb_smssendto Customer|Prospect|Lead|Customer Contact, qdb_language, qdb_otp, qdb_whatsapptemplate, plus cifno/contact/lead/prospect recipient lookups) — but 0 rows, 0 workflows on fax, and the ONLY plugin step is Microsoft own LeadManagement.SendFax on the Send message. A sweep of 400 workflows and 200 assemblies found every SMS-related item to be Microsoft (Omnichannel/Field Service/Sales Insights). QDB dispatch is NOT INSTALLED here (KI-83). (2) WhatsApp discriminator cannot be established — qdb_whatsapptemplate is plausible but unconfirmed with zero rows (KI-78). (3) Email is standard Dynamics, 0 rows, no DCP-relevant customisation; qdb_reports on email points at the training/trade report entity, NOT letters. (4) qdb_communicationtemplate is fully provisioned with the DCP schema incl. qdb_externaltemplateref — 0 rows. (5) CONTACT HOLD SOURCE DOES NOT EXIST: qdb_stopcontact/qdb_deceasedflag/qdb_dateofdeath/qdb_specialhandling are absent from contact and account; qdb_contactholdrulesetcode is null on both platform configurations; deceased facts live on the SNAPSHOT (qdb_isdeceasedperqcb = the 724 imported flags, MIS data only). Gate therefore FAILS CLOSED (KI-79) — BLOCKS ALL SENDS until QDB nominates the source. (6) Report Engine IS installed (qdb_reportdefinition/layout/version/exportsetting/executionlog) but its 13 definitions are all samples/demos and no SSRS report matches letter/warning/notice/demand/collection — warning-letter mechanism undecided, isolated so it blocks nothing else (KI-81). (7) qdb_privsendsms exists among a family of qdb_priv_* marker entities — QDB authorisation convention, to be checked rather than reinvented (KI-82). (8) qdb_communication ALREADY EXISTS as a Partner Bank activity (qdb_message + qdb_partnerbank) — not created, and deliberately NOT repurposed. NEW: KI-78..KI-83. STATUS LANGUAGE FOR THIS PHASE: Record Creation Proven — Delivery Unproven on this organisation. AWAITING CLIENT DECISION on KI-79 and KI-83 before implementation begins. ||| REVISED 2026-09-20 — QDB supplied the confirmed implementation details. SMS = faxnumber + qdb_message_body + qdb_sender (NO other fields). WhatsApp = same three PLUS qdb_language + qdb_whatsapptemplate + qdb_otp, which are WhatsApp-only — KI-78 CLOSED by confirmation, not inference. Email = standard Dynamics Email with native ActivityParty + regarding; no SMTP/Graph/Exchange and no custom entity. KI-83 REVISED: the QDB SMS/WhatsApp Custom Workflow Activity EXISTS ON-PREM and is merely absent from the Cloud dev org — architecture approved (Workspace &gt; Communication service &gt; Fax/Email &gt; existing QDB CWA &gt; provider); DCP builds NO dispatcher; Cloud proof is record creation + read-back only and delivery is explicitly NOT Cloud-runtime-tested. WARNING LETTERS REMOVED FROM SCOPE — KI-81 closed as a scope decision, not a blocker; no Report Engine config, templates, UI, SSRS, document generation or further investigation. BULK SMS + BULK EMAIL ADDED (no bulk WhatsApp). KI-84 NEW: no existing QDB or native mechanism can safely carry a resumable bulk job — qdb_publish_job has 277 LIVE rows and belongs to the Dynamic Form Engine, qdb_workflowtracker has no checkpoint/batch/filter/per-recipient result, qdb_tcs_job_status/qdb_processstatus/qdb_wf_runtime_context are empty shells, and native bulkoperation/Quick Campaign is bound to marketing lists with no controllable continuation. Structural safety needs NO entity (deterministic per-recipient ids + If-None-Match); only cross-session RESUMPTION does, so a minimal qdb_communicationrun is PROPOSED FOR APPROVAL and NOT created. ESTIMATE CORRECTED: the discovery package list summed to 16.00h while stating 13.00h — the total had been judged rather than summed. Revised implementation baseline = 22.00 effective hours across 15 packages (discovery 13.00h retained above for traceability). Expected completion = start + 22.00 EFFECTIVE hours, not a wall-clock date. HIGHEST RISK: fax/email are NATIVE activity entities and upsert-by-id is NOT established — WP3 spikes it before any send path is built, because a duplicate SMS reaches the customer twice. Plan: docs/Phase7_Plan.md. Contract: docs/Phase7_CommunicationContract.md PART TWO.</v>
       </c>
     </row>
     <row r="10">

--- a/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
+++ b/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Communications &amp; Warning Letters. Estimated 13.00 AI-assisted effective execution hours; expected completion = start + 13.00 EFFECTIVE execution hours (a working-time figure, not a wall-clock date — the span since the recorded start includes a long idle gap that is not execution time; discovery itself was ~30 minutes of tool work). Wall clock at discovery close: 2026-09-20 07:44 (+03:00). Branch feat/dcp-phase7-communications from the accepted Phase 6 baseline 7ebf1381. DISCOVERY COMPLETE 2026-09-19, NO CODE WRITTEN — docs/Phase7_CommunicationContract.md. FINDINGS: (1) fax carries a REAL, coherent QDB SMS schema (31 qdb_ columns: qdb_message_body, qdb_sms_id, qdb_sender QDB|NFG, qdb_sendernumber +97444300000, qdb_smssendto Customer|Prospect|Lead|Customer Contact, qdb_language, qdb_otp, qdb_whatsapptemplate, plus cifno/contact/lead/prospect recipient lookups) — but 0 rows, 0 workflows on fax, and the ONLY plugin step is Microsoft own LeadManagement.SendFax on the Send message. A sweep of 400 workflows and 200 assemblies found every SMS-related item to be Microsoft (Omnichannel/Field Service/Sales Insights). QDB dispatch is NOT INSTALLED here (KI-83). (2) WhatsApp discriminator cannot be established — qdb_whatsapptemplate is plausible but unconfirmed with zero rows (KI-78). (3) Email is standard Dynamics, 0 rows, no DCP-relevant customisation; qdb_reports on email points at the training/trade report entity, NOT letters. (4) qdb_communicationtemplate is fully provisioned with the DCP schema incl. qdb_externaltemplateref — 0 rows. (5) CONTACT HOLD SOURCE DOES NOT EXIST: qdb_stopcontact/qdb_deceasedflag/qdb_dateofdeath/qdb_specialhandling are absent from contact and account; qdb_contactholdrulesetcode is null on both platform configurations; deceased facts live on the SNAPSHOT (qdb_isdeceasedperqcb = the 724 imported flags, MIS data only). Gate therefore FAILS CLOSED (KI-79) — BLOCKS ALL SENDS until QDB nominates the source. (6) Report Engine IS installed (qdb_reportdefinition/layout/version/exportsetting/executionlog) but its 13 definitions are all samples/demos and no SSRS report matches letter/warning/notice/demand/collection — warning-letter mechanism undecided, isolated so it blocks nothing else (KI-81). (7) qdb_privsendsms exists among a family of qdb_priv_* marker entities — QDB authorisation convention, to be checked rather than reinvented (KI-82). (8) qdb_communication ALREADY EXISTS as a Partner Bank activity (qdb_message + qdb_partnerbank) — not created, and deliberately NOT repurposed. NEW: KI-78..KI-83. STATUS LANGUAGE FOR THIS PHASE: Record Creation Proven — Delivery Unproven on this organisation. AWAITING CLIENT DECISION on KI-79 and KI-83 before implementation begins. ||| REVISED 2026-09-20 — QDB supplied the confirmed implementation details. SMS = faxnumber + qdb_message_body + qdb_sender (NO other fields). WhatsApp = same three PLUS qdb_language + qdb_whatsapptemplate + qdb_otp, which are WhatsApp-only — KI-78 CLOSED by confirmation, not inference. Email = standard Dynamics Email with native ActivityParty + regarding; no SMTP/Graph/Exchange and no custom entity. KI-83 REVISED: the QDB SMS/WhatsApp Custom Workflow Activity EXISTS ON-PREM and is merely absent from the Cloud dev org — architecture approved (Workspace &gt; Communication service &gt; Fax/Email &gt; existing QDB CWA &gt; provider); DCP builds NO dispatcher; Cloud proof is record creation + read-back only and delivery is explicitly NOT Cloud-runtime-tested. WARNING LETTERS REMOVED FROM SCOPE — KI-81 closed as a scope decision, not a blocker; no Report Engine config, templates, UI, SSRS, document generation or further investigation. BULK SMS + BULK EMAIL ADDED (no bulk WhatsApp). KI-84 NEW: no existing QDB or native mechanism can safely carry a resumable bulk job — qdb_publish_job has 277 LIVE rows and belongs to the Dynamic Form Engine, qdb_workflowtracker has no checkpoint/batch/filter/per-recipient result, qdb_tcs_job_status/qdb_processstatus/qdb_wf_runtime_context are empty shells, and native bulkoperation/Quick Campaign is bound to marketing lists with no controllable continuation. Structural safety needs NO entity (deterministic per-recipient ids + If-None-Match); only cross-session RESUMPTION does, so a minimal qdb_communicationrun is PROPOSED FOR APPROVAL and NOT created. ESTIMATE CORRECTED: the discovery package list summed to 16.00h while stating 13.00h — the total had been judged rather than summed. Revised implementation baseline = 22.00 effective hours across 15 packages (discovery 13.00h retained above for traceability). Expected completion = start + 22.00 EFFECTIVE hours, not a wall-clock date. HIGHEST RISK: fax/email are NATIVE activity entities and upsert-by-id is NOT established — WP3 spikes it before any send path is built, because a duplicate SMS reaches the customer twice. Plan: docs/Phase7_Plan.md. Contract: docs/Phase7_CommunicationContract.md PART TWO.</v>
+        <v>Communications &amp; Warning Letters. Estimated 13.00 AI-assisted effective execution hours; expected completion = start + 13.00 EFFECTIVE execution hours (a working-time figure, not a wall-clock date — the span since the recorded start includes a long idle gap that is not execution time; discovery itself was ~30 minutes of tool work). Wall clock at discovery close: 2026-09-20 07:44 (+03:00). Branch feat/dcp-phase7-communications from the accepted Phase 6 baseline 7ebf1381. DISCOVERY COMPLETE 2026-09-19, NO CODE WRITTEN — docs/Phase7_CommunicationContract.md. FINDINGS: (1) fax carries a REAL, coherent QDB SMS schema (31 qdb_ columns: qdb_message_body, qdb_sms_id, qdb_sender QDB|NFG, qdb_sendernumber +97444300000, qdb_smssendto Customer|Prospect|Lead|Customer Contact, qdb_language, qdb_otp, qdb_whatsapptemplate, plus cifno/contact/lead/prospect recipient lookups) — but 0 rows, 0 workflows on fax, and the ONLY plugin step is Microsoft own LeadManagement.SendFax on the Send message. A sweep of 400 workflows and 200 assemblies found every SMS-related item to be Microsoft (Omnichannel/Field Service/Sales Insights). QDB dispatch is NOT INSTALLED here (KI-83). (2) WhatsApp discriminator cannot be established — qdb_whatsapptemplate is plausible but unconfirmed with zero rows (KI-78). (3) Email is standard Dynamics, 0 rows, no DCP-relevant customisation; qdb_reports on email points at the training/trade report entity, NOT letters. (4) qdb_communicationtemplate is fully provisioned with the DCP schema incl. qdb_externaltemplateref — 0 rows. (5) CONTACT HOLD SOURCE DOES NOT EXIST: qdb_stopcontact/qdb_deceasedflag/qdb_dateofdeath/qdb_specialhandling are absent from contact and account; qdb_contactholdrulesetcode is null on both platform configurations; deceased facts live on the SNAPSHOT (qdb_isdeceasedperqcb = the 724 imported flags, MIS data only). Gate therefore FAILS CLOSED (KI-79) — BLOCKS ALL SENDS until QDB nominates the source. (6) Report Engine IS installed (qdb_reportdefinition/layout/version/exportsetting/executionlog) but its 13 definitions are all samples/demos and no SSRS report matches letter/warning/notice/demand/collection — warning-letter mechanism undecided, isolated so it blocks nothing else (KI-81). (7) qdb_privsendsms exists among a family of qdb_priv_* marker entities — QDB authorisation convention, to be checked rather than reinvented (KI-82). (8) qdb_communication ALREADY EXISTS as a Partner Bank activity (qdb_message + qdb_partnerbank) — not created, and deliberately NOT repurposed. NEW: KI-78..KI-83. STATUS LANGUAGE FOR THIS PHASE: Record Creation Proven — Delivery Unproven on this organisation. AWAITING CLIENT DECISION on KI-79 and KI-83 before implementation begins. ||| REVISED 2026-09-20 — QDB supplied the confirmed implementation details. SMS = faxnumber + qdb_message_body + qdb_sender (NO other fields). WhatsApp = same three PLUS qdb_language + qdb_whatsapptemplate + qdb_otp, which are WhatsApp-only — KI-78 CLOSED by confirmation, not inference. Email = standard Dynamics Email with native ActivityParty + regarding; no SMTP/Graph/Exchange and no custom entity. KI-83 REVISED: the QDB SMS/WhatsApp Custom Workflow Activity EXISTS ON-PREM and is merely absent from the Cloud dev org — architecture approved (Workspace &gt; Communication service &gt; Fax/Email &gt; existing QDB CWA &gt; provider); DCP builds NO dispatcher; Cloud proof is record creation + read-back only and delivery is explicitly NOT Cloud-runtime-tested. WARNING LETTERS REMOVED FROM SCOPE — KI-81 closed as a scope decision, not a blocker; no Report Engine config, templates, UI, SSRS, document generation or further investigation. BULK SMS + BULK EMAIL ADDED (no bulk WhatsApp). KI-84 NEW: no existing QDB or native mechanism can safely carry a resumable bulk job — qdb_publish_job has 277 LIVE rows and belongs to the Dynamic Form Engine, qdb_workflowtracker has no checkpoint/batch/filter/per-recipient result, qdb_tcs_job_status/qdb_processstatus/qdb_wf_runtime_context are empty shells, and native bulkoperation/Quick Campaign is bound to marketing lists with no controllable continuation. Structural safety needs NO entity (deterministic per-recipient ids + If-None-Match); only cross-session RESUMPTION does, so a minimal qdb_communicationrun is PROPOSED FOR APPROVAL and NOT created. ESTIMATE CORRECTED: the discovery package list summed to 16.00h while stating 13.00h — the total had been judged rather than summed. Revised implementation baseline = 22.00 effective hours across 15 packages (discovery 13.00h retained above for traceability). Expected completion = start + 22.00 EFFECTIVE hours, not a wall-clock date. HIGHEST RISK: fax/email are NATIVE activity entities and upsert-by-id is NOT established — WP3 spikes it before any send path is built, because a duplicate SMS reaches the customer twice. Plan: docs/Phase7_Plan.md. Contract: docs/Phase7_CommunicationContract.md PART TWO. ||| 2026-09-20 WP3 COMPLETE: upsert-by-id PROVEN on native fax AND email (17/17) — client-chosen PK + If-None-Match works, repeat refused, refused repeat does NOT overwrite, and an unguarded PATCH DOES create (so the guard is load-bearing). Bulk idempotency is therefore structural. WP1 COMPLETE: communication.ts (QDB-confirmed minimal field contracts; WhatsApp discriminated by OMISSION of its three fields; ONE eligibility gate for single AND bulk; donotfax governs SMS+WhatsApp since both leave via Fax; creditonhold deliberately NOT consulted; ContactHoldVerdict is an injected port so KI-79 drops in with no call-site change) + communicationIdentity.ts (uuidv5(run|recipient|channel), SHA-1 hand-written because @dcp/domain runs in the BROWSER and must not import node: per KI-63 — the first draft used node:crypto and would have broken at runtime; pinned to 3 vectors verified against Node crypto incl. a 500-char name crossing the 64-byte block boundary). 386 domain tests. DISCOVERED: account has NO mobilephone (telephone1/2 only) where contact has it — HL/BFD asymmetry absorbed by the recipient resolver so no component branches. ESTIMATE REVISION RECORDED (not silent): 22.00h baseline + 0.50h for qdb_communicationrun provisioning = 22.50h forecast; reason = the KI-84 entity was scoped in WP11 as design, not provisioning; timestamp 2026-09-20 (+03:00). AWAITING: final approval of docs/Phase7_CommunicationRun_SchemaProposal.md before the entity is created — 1 entity, 14 columns, 1 lookup, NO child entity (measured: the whole 4,363-case book freezes to 140.6 KB vs a 1,048,576-char Memo ceiling of ~31,775 ids = 7.3x headroom; runs above the ceiling are REFUSED at composition, never truncated).</v>
       </c>
     </row>
     <row r="10">

--- a/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
+++ b/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
@@ -519,7 +519,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F76"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1781,11 +1781,249 @@
         <v>needs an authenticated interactive CRM session — NOT claimed as passed</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>— Phase 7 closure baseline (accepted 2026-09-21) —</v>
+      </c>
+      <c r="B65" t="str">
+        <v/>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>TS vitest — @dcp/domain</v>
+      </c>
+      <c r="B66">
+        <v>454</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="F66" t="str">
+        <v>PHASE 7 CLOSURE BASELINE — actually executed at closure, uncached. Supersedes the 1,210 figure.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>TS vitest — @dcp/web</v>
+      </c>
+      <c r="B67">
+        <v>436</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="F67" t="str">
+        <v>PHASE 7 CLOSURE BASELINE — actually executed at closure, uncached. Supersedes the 1,210 figure. WP12 added 39 (397 -&gt; 436).</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>TS vitest — @dcp/api</v>
+      </c>
+      <c r="B68">
+        <v>325</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="F68" t="str">
+        <v>PHASE 7 CLOSURE BASELINE — actually executed at closure, uncached. Supersedes the 1,210 figure. The earlier 313 was a stale turbo cache entry.</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>TS vitest — @dcp/dataverse-client</v>
+      </c>
+      <c r="B69">
+        <v>32</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="F69" t="str">
+        <v>PHASE 7 CLOSURE BASELINE — actually executed at closure, uncached. Supersedes the 1,210 figure.</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>TS vitest — @dcp/auth-adapters</v>
+      </c>
+      <c r="B70">
+        <v>14</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="F70" t="str">
+        <v>PHASE 7 CLOSURE BASELINE — actually executed at closure, uncached. Supersedes the 1,210 figure.</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>TypeScript total</v>
+      </c>
+      <c r="B71">
+        <v>1261</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="F71" t="str">
+        <v>ACCEPTED CLOSURE BASELINE</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Tooling — node:test (crm/scripts/lib)</v>
+      </c>
+      <c r="B72">
+        <v>10</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="F72" t="str">
+        <v>PHASE 7 CLOSURE BASELINE — actually executed at closure, uncached. Supersedes the 1,210 figure.</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>C# xUnit — Qdb.DebtCollection.Plugins.Tests</v>
+      </c>
+      <c r="B73">
+        <v>147</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="F73" t="str">
+        <v>RE-RUN at closure rather than carried forward, at QDB instruction.</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Browser QA — bulk gates 1-14 (org5869857f)</v>
+      </c>
+      <c r="B74">
+        <v>14</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Officer journey on the deployed workspace. docs/evidence/Phase7_WP12_browser_qa.md</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Live cleanup — qa-clean-bulk-run.mts</v>
+      </c>
+      <c r="B75">
+        <v>8</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Derived ids, re-read to prove removal; 0 run/Fax/Email residue afterwards.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Web resource deploy — deploy-workspace-webresource.mjs</v>
+      </c>
+      <c r="B76">
+        <v>11</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Uploaded, published and read back byte for byte.</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F63"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F76"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1962,16 +2200,16 @@
         <v>Communication Center</v>
       </c>
       <c r="C9" t="str">
-        <v>In Progress — implementation baseline approved; single-channel unblocked, bulk resumability awaiting KI-84 schema approval</v>
+        <v>Complete — CLOSED; formally accepted by QDB 2026-09-21</v>
       </c>
       <c r="D9" t="str">
         <v>2026-09-19 21:53:42 (+03:00 Asia/Qatar)</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>2026-09-21 08:41 (+03:00 Asia/Qatar)</v>
       </c>
       <c r="F9" t="str">
-        <v>Communications &amp; Warning Letters. Estimated 13.00 AI-assisted effective execution hours; expected completion = start + 13.00 EFFECTIVE execution hours (a working-time figure, not a wall-clock date — the span since the recorded start includes a long idle gap that is not execution time; discovery itself was ~30 minutes of tool work). Wall clock at discovery close: 2026-09-20 07:44 (+03:00). Branch feat/dcp-phase7-communications from the accepted Phase 6 baseline 7ebf1381. DISCOVERY COMPLETE 2026-09-19, NO CODE WRITTEN — docs/Phase7_CommunicationContract.md. FINDINGS: (1) fax carries a REAL, coherent QDB SMS schema (31 qdb_ columns: qdb_message_body, qdb_sms_id, qdb_sender QDB|NFG, qdb_sendernumber +97444300000, qdb_smssendto Customer|Prospect|Lead|Customer Contact, qdb_language, qdb_otp, qdb_whatsapptemplate, plus cifno/contact/lead/prospect recipient lookups) — but 0 rows, 0 workflows on fax, and the ONLY plugin step is Microsoft own LeadManagement.SendFax on the Send message. A sweep of 400 workflows and 200 assemblies found every SMS-related item to be Microsoft (Omnichannel/Field Service/Sales Insights). QDB dispatch is NOT INSTALLED here (KI-83). (2) WhatsApp discriminator cannot be established — qdb_whatsapptemplate is plausible but unconfirmed with zero rows (KI-78). (3) Email is standard Dynamics, 0 rows, no DCP-relevant customisation; qdb_reports on email points at the training/trade report entity, NOT letters. (4) qdb_communicationtemplate is fully provisioned with the DCP schema incl. qdb_externaltemplateref — 0 rows. (5) CONTACT HOLD SOURCE DOES NOT EXIST: qdb_stopcontact/qdb_deceasedflag/qdb_dateofdeath/qdb_specialhandling are absent from contact and account; qdb_contactholdrulesetcode is null on both platform configurations; deceased facts live on the SNAPSHOT (qdb_isdeceasedperqcb = the 724 imported flags, MIS data only). Gate therefore FAILS CLOSED (KI-79) — BLOCKS ALL SENDS until QDB nominates the source. (6) Report Engine IS installed (qdb_reportdefinition/layout/version/exportsetting/executionlog) but its 13 definitions are all samples/demos and no SSRS report matches letter/warning/notice/demand/collection — warning-letter mechanism undecided, isolated so it blocks nothing else (KI-81). (7) qdb_privsendsms exists among a family of qdb_priv_* marker entities — QDB authorisation convention, to be checked rather than reinvented (KI-82). (8) qdb_communication ALREADY EXISTS as a Partner Bank activity (qdb_message + qdb_partnerbank) — not created, and deliberately NOT repurposed. NEW: KI-78..KI-83. STATUS LANGUAGE FOR THIS PHASE: Record Creation Proven — Delivery Unproven on this organisation. AWAITING CLIENT DECISION on KI-79 and KI-83 before implementation begins. ||| REVISED 2026-09-20 — QDB supplied the confirmed implementation details. SMS = faxnumber + qdb_message_body + qdb_sender (NO other fields). WhatsApp = same three PLUS qdb_language + qdb_whatsapptemplate + qdb_otp, which are WhatsApp-only — KI-78 CLOSED by confirmation, not inference. Email = standard Dynamics Email with native ActivityParty + regarding; no SMTP/Graph/Exchange and no custom entity. KI-83 REVISED: the QDB SMS/WhatsApp Custom Workflow Activity EXISTS ON-PREM and is merely absent from the Cloud dev org — architecture approved (Workspace &gt; Communication service &gt; Fax/Email &gt; existing QDB CWA &gt; provider); DCP builds NO dispatcher; Cloud proof is record creation + read-back only and delivery is explicitly NOT Cloud-runtime-tested. WARNING LETTERS REMOVED FROM SCOPE — KI-81 closed as a scope decision, not a blocker; no Report Engine config, templates, UI, SSRS, document generation or further investigation. BULK SMS + BULK EMAIL ADDED (no bulk WhatsApp). KI-84 NEW: no existing QDB or native mechanism can safely carry a resumable bulk job — qdb_publish_job has 277 LIVE rows and belongs to the Dynamic Form Engine, qdb_workflowtracker has no checkpoint/batch/filter/per-recipient result, qdb_tcs_job_status/qdb_processstatus/qdb_wf_runtime_context are empty shells, and native bulkoperation/Quick Campaign is bound to marketing lists with no controllable continuation. Structural safety needs NO entity (deterministic per-recipient ids + If-None-Match); only cross-session RESUMPTION does, so a minimal qdb_communicationrun is PROPOSED FOR APPROVAL and NOT created. ESTIMATE CORRECTED: the discovery package list summed to 16.00h while stating 13.00h — the total had been judged rather than summed. Revised implementation baseline = 22.00 effective hours across 15 packages (discovery 13.00h retained above for traceability). Expected completion = start + 22.00 EFFECTIVE hours, not a wall-clock date. HIGHEST RISK: fax/email are NATIVE activity entities and upsert-by-id is NOT established — WP3 spikes it before any send path is built, because a duplicate SMS reaches the customer twice. Plan: docs/Phase7_Plan.md. Contract: docs/Phase7_CommunicationContract.md PART TWO. ||| 2026-09-20 WP3 COMPLETE: upsert-by-id PROVEN on native fax AND email (17/17) — client-chosen PK + If-None-Match works, repeat refused, refused repeat does NOT overwrite, and an unguarded PATCH DOES create (so the guard is load-bearing). Bulk idempotency is therefore structural. WP1 COMPLETE: communication.ts (QDB-confirmed minimal field contracts; WhatsApp discriminated by OMISSION of its three fields; ONE eligibility gate for single AND bulk; donotfax governs SMS+WhatsApp since both leave via Fax; creditonhold deliberately NOT consulted; ContactHoldVerdict is an injected port so KI-79 drops in with no call-site change) + communicationIdentity.ts (uuidv5(run|recipient|channel), SHA-1 hand-written because @dcp/domain runs in the BROWSER and must not import node: per KI-63 — the first draft used node:crypto and would have broken at runtime; pinned to 3 vectors verified against Node crypto incl. a 500-char name crossing the 64-byte block boundary). 386 domain tests. DISCOVERED: account has NO mobilephone (telephone1/2 only) where contact has it — HL/BFD asymmetry absorbed by the recipient resolver so no component branches. ESTIMATE REVISION RECORDED (not silent): 22.00h baseline + 0.50h for qdb_communicationrun provisioning = 22.50h forecast; reason = the KI-84 entity was scoped in WP11 as design, not provisioning; timestamp 2026-09-20 (+03:00). AWAITING: final approval of docs/Phase7_CommunicationRun_SchemaProposal.md before the entity is created — 1 entity, 14 columns, 1 lookup, NO child entity (measured: the whole 4,363-case book freezes to 140.6 KB vs a 1,048,576-char Memo ceiling of ~31,775 ids = 7.3x headroom; runs above the ceiling are REFUSED at composition, never truncated).</v>
+        <v>Communications &amp; Warning Letters. Estimated 13.00 AI-assisted effective execution hours; expected completion = start + 13.00 EFFECTIVE execution hours (a working-time figure, not a wall-clock date — the span since the recorded start includes a long idle gap that is not execution time; discovery itself was ~30 minutes of tool work). Wall clock at discovery close: 2026-09-20 07:44 (+03:00). Branch feat/dcp-phase7-communications from the accepted Phase 6 baseline 7ebf1381. DISCOVERY COMPLETE 2026-09-19, NO CODE WRITTEN — docs/Phase7_CommunicationContract.md. FINDINGS: (1) fax carries a REAL, coherent QDB SMS schema (31 qdb_ columns: qdb_message_body, qdb_sms_id, qdb_sender QDB|NFG, qdb_sendernumber +97444300000, qdb_smssendto Customer|Prospect|Lead|Customer Contact, qdb_language, qdb_otp, qdb_whatsapptemplate, plus cifno/contact/lead/prospect recipient lookups) — but 0 rows, 0 workflows on fax, and the ONLY plugin step is Microsoft own LeadManagement.SendFax on the Send message. A sweep of 400 workflows and 200 assemblies found every SMS-related item to be Microsoft (Omnichannel/Field Service/Sales Insights). QDB dispatch is NOT INSTALLED here (KI-83). (2) WhatsApp discriminator cannot be established — qdb_whatsapptemplate is plausible but unconfirmed with zero rows (KI-78). (3) Email is standard Dynamics, 0 rows, no DCP-relevant customisation; qdb_reports on email points at the training/trade report entity, NOT letters. (4) qdb_communicationtemplate is fully provisioned with the DCP schema incl. qdb_externaltemplateref — 0 rows. (5) CONTACT HOLD SOURCE DOES NOT EXIST: qdb_stopcontact/qdb_deceasedflag/qdb_dateofdeath/qdb_specialhandling are absent from contact and account; qdb_contactholdrulesetcode is null on both platform configurations; deceased facts live on the SNAPSHOT (qdb_isdeceasedperqcb = the 724 imported flags, MIS data only). Gate therefore FAILS CLOSED (KI-79) — BLOCKS ALL SENDS until QDB nominates the source. (6) Report Engine IS installed (qdb_reportdefinition/layout/version/exportsetting/executionlog) but its 13 definitions are all samples/demos and no SSRS report matches letter/warning/notice/demand/collection — warning-letter mechanism undecided, isolated so it blocks nothing else (KI-81). (7) qdb_privsendsms exists among a family of qdb_priv_* marker entities — QDB authorisation convention, to be checked rather than reinvented (KI-82). (8) qdb_communication ALREADY EXISTS as a Partner Bank activity (qdb_message + qdb_partnerbank) — not created, and deliberately NOT repurposed. NEW: KI-78..KI-83. STATUS LANGUAGE FOR THIS PHASE: Record Creation Proven — Delivery Unproven on this organisation. AWAITING CLIENT DECISION on KI-79 and KI-83 before implementation begins. ||| REVISED 2026-09-20 — QDB supplied the confirmed implementation details. SMS = faxnumber + qdb_message_body + qdb_sender (NO other fields). WhatsApp = same three PLUS qdb_language + qdb_whatsapptemplate + qdb_otp, which are WhatsApp-only — KI-78 CLOSED by confirmation, not inference. Email = standard Dynamics Email with native ActivityParty + regarding; no SMTP/Graph/Exchange and no custom entity. KI-83 REVISED: the QDB SMS/WhatsApp Custom Workflow Activity EXISTS ON-PREM and is merely absent from the Cloud dev org — architecture approved (Workspace &gt; Communication service &gt; Fax/Email &gt; existing QDB CWA &gt; provider); DCP builds NO dispatcher; Cloud proof is record creation + read-back only and delivery is explicitly NOT Cloud-runtime-tested. WARNING LETTERS REMOVED FROM SCOPE — KI-81 closed as a scope decision, not a blocker; no Report Engine config, templates, UI, SSRS, document generation or further investigation. BULK SMS + BULK EMAIL ADDED (no bulk WhatsApp). KI-84 NEW: no existing QDB or native mechanism can safely carry a resumable bulk job — qdb_publish_job has 277 LIVE rows and belongs to the Dynamic Form Engine, qdb_workflowtracker has no checkpoint/batch/filter/per-recipient result, qdb_tcs_job_status/qdb_processstatus/qdb_wf_runtime_context are empty shells, and native bulkoperation/Quick Campaign is bound to marketing lists with no controllable continuation. Structural safety needs NO entity (deterministic per-recipient ids + If-None-Match); only cross-session RESUMPTION does, so a minimal qdb_communicationrun is PROPOSED FOR APPROVAL and NOT created. ESTIMATE CORRECTED: the discovery package list summed to 16.00h while stating 13.00h — the total had been judged rather than summed. Revised implementation baseline = 22.00 effective hours across 15 packages (discovery 13.00h retained above for traceability). Expected completion = start + 22.00 EFFECTIVE hours, not a wall-clock date. HIGHEST RISK: fax/email are NATIVE activity entities and upsert-by-id is NOT established — WP3 spikes it before any send path is built, because a duplicate SMS reaches the customer twice. Plan: docs/Phase7_Plan.md. Contract: docs/Phase7_CommunicationContract.md PART TWO. ||| 2026-09-20 WP3 COMPLETE: upsert-by-id PROVEN on native fax AND email (17/17) — client-chosen PK + If-None-Match works, repeat refused, refused repeat does NOT overwrite, and an unguarded PATCH DOES create (so the guard is load-bearing). Bulk idempotency is therefore structural. WP1 COMPLETE: communication.ts (QDB-confirmed minimal field contracts; WhatsApp discriminated by OMISSION of its three fields; ONE eligibility gate for single AND bulk; donotfax governs SMS+WhatsApp since both leave via Fax; creditonhold deliberately NOT consulted; ContactHoldVerdict is an injected port so KI-79 drops in with no call-site change) + communicationIdentity.ts (uuidv5(run|recipient|channel), SHA-1 hand-written because @dcp/domain runs in the BROWSER and must not import node: per KI-63 — the first draft used node:crypto and would have broken at runtime; pinned to 3 vectors verified against Node crypto incl. a 500-char name crossing the 64-byte block boundary). 386 domain tests. DISCOVERED: account has NO mobilephone (telephone1/2 only) where contact has it — HL/BFD asymmetry absorbed by the recipient resolver so no component branches. ESTIMATE REVISION RECORDED (not silent): 22.00h baseline + 0.50h for qdb_communicationrun provisioning = 22.50h forecast; reason = the KI-84 entity was scoped in WP11 as design, not provisioning; timestamp 2026-09-20 (+03:00). AWAITING: final approval of docs/Phase7_CommunicationRun_SchemaProposal.md before the entity is created — 1 entity, 14 columns, 1 lookup, NO child entity (measured: the whole 4,363-case book freezes to 140.6 KB vs a 1,048,576-char Memo ceiling of ~31,775 ids = 7.3x headroom; runs above the ceiling are REFUSED at composition, never truncated). ||| PHASE 7 CLOSED 2026-09-21 — FORMALLY ACCEPTED BY QDB. ACCEPTED SCOPE: single SMS / WhatsApp / Email officer-usable and Cloud native-record runtime validated; Bulk SMS and Bulk Email officer-usable and runtime validated. OUT OF SCOPE: Bulk WhatsApp, Warning Letters. WP12 (Bulk Communication UI) was MISSING from the 2026-09-20 closure draft and was built, deployed and browser-validated afterwards: Communication &gt; Bulk SMS &amp; Email; selected-case and filter population modes; target count before confirmation; no full population loaded into the browser; approved templates only; rendered preview; frozen population/content confirmation; progress/status; reopen; refresh/recovery through the persisted run; resume/retry; safe stop/cancel. 14/14 browser QA gates PASS on org5869857f as Mohammad Salman; 2 Fax + 2 Email verified directly against Dataverse with exactly one recipient party each; retry created no duplicate; history reflected the communications; cleanup 8/8 by derived id; zero transient run/Fax/Email residue. Evidence: docs/evidence/Phase7_WP12_browser_qa.md. KI-96 (cross-phase): Xrm.WebApi NEVER returns @odata.count, so every count-bearing surface had been dead since Phase 5 while 436 tests passed over it — the fake Xrm returned a count the real one never sends. Counting now goes through the transport and an unknown count is null, NEVER 0. Real-transport regression coverage preserved. KI-84 CLOSED (qdb_communicationrun approved, provisioned 5/5, now operated end to end). KI-97 NEW, accepted as UX/routing debt: a top-level browser reload returns the workspace to its default view because a web resource owns only its own URL fragment — persisted run state is NOT lost and the officer reopens from the run list. ADR-DCP-20 written. CLOSURE BASELINE, ACTUALLY EXECUTED (the earlier 1,210 figure contained a cached api count and is SUPERSEDED): TypeScript 1,261 (domain 454, web 436, api 325, dataverse-client 32, auth-adapters 14), tooling 10, C# 147; 0 failed, 0 skipped; type-check clean. Deploy+publish 11/11 byte-for-byte. RUNTIME STATUS PRESERVED: Cloud SMS/WhatsApp Native Record Creation Proven — External Delivery Unproven; Dynamics 365 CE 9.1 On-Prem Compatible by Design — Phase 7 Runtime Validation Pending. Neither may be upgraded without corresponding runtime evidence. OPEN AND UNRESOLVED BY CLOSURE: KI-79, KI-83, KI-76, KI-95, KI-97, and every other previously open KI under its existing status. TIMING: baseline 22.50h unchanged; WP12 estimate 2.00h, actual ~11h27m; Phase 7 total effective ~18h42m; variance -3.80h against the original baseline — estimation calibration information, NOT a productivity claim. PHASE 8 NOT AUTHORISED: no branch, no discovery, no implementation. The Phase 8 prerequisite review — KI-71 above all (no Collection Activity -&gt; Strategy Action provenance) — must be explicitly authorised first.</v>
       </c>
     </row>
     <row r="10">
@@ -2055,8 +2293,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
   </ignoredErrors>

--- a/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
+++ b/projects/debtcollection/DebtCollection_Project_Tracker.xlsx
@@ -2217,19 +2217,19 @@
         <v>Phase 8</v>
       </c>
       <c r="B10" t="str">
-        <v>Strategy automation &amp; assignment</v>
+        <v>Strategy automation, assignment &amp; escalation</v>
       </c>
       <c r="C10" t="str">
-        <v>Not Started</v>
+        <v>In Progress - WP1 discovery COMPLETE; 2 decisions outstanding (Legal, Restructuring); unblocked packages proceeding</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>2026-09-21 09:14:10 (+03:00 Asia/Qatar)</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>PHASE 8 authorised 2026-09-21 from the accepted Phase 7 baseline 7c92463d. Branch feat/dcp-phase8-strategy-automation. ||| ESTIMATE 36.50 AI-assisted effective execution hours, SUMMED from 16 packages (not judged). Expected completion = start + 36.50 EFFECTIVE hours, deliberately not a wall-clock date. ||| WP1 DISCOVERY COMPLETE - read-only probe of org5869857f, re-runnable at crm/scripts/probe-phase8-discovery.mts; write-up docs/Phase8_Discovery.md. Nothing created, updated or deleted. ||| KI-71 CONFIRMED BY METADATA: qdb_collectionactivity has ZERO lookups to qdb_strategyaction and NO alternate keys. Configuration available to automate against: 2 strategies, 4 strategy actions, 12 activity types, 30 outcomes. ||| KI-71 DESIGN (WP2): two optional additive columns on qdb_collectionactivity - qdb_strategyactionid (lookup to qdb_strategyaction) for provenance, and qdb_origin (choice Manual / Strategy generated) so origin is STATED not inferred. Idempotency is NOT a column: strategy-generated work takes activityId = uuidv5(caseId | episodeNumber | strategyActionId | evaluationContext) with If-None-Match:* per ADR-DCP-20. Backfill leaves both null - asserting historic activities were Manual would invent history. Cloud and On-Prem identical. No QDB business semantics changed, so provisioned under authorisation section 3 rather than escalated. ||| LEGAL - qdb_qdblegal (Litigation Request) EXISTS: 158 attributes, OrganizationOwned (no ownerid), audit on, NO alternate keys. Business-required on create: qdb_casetype, qdb_caseagainst, qdb_caseinitiatedby, qdb_summaryjustification. BUT all 32 registered plugin steps are MICROSOFT platform internals (ObjectModel Implementation, Archive/Retain) - ZERO QDB custom plugins - and ZERO workflows/BPF/actions have it as primary entity. The preferred option B (call an existing supported business entry point) DOES NOT EXIST on this org. Also its customer lookups qdb_customer and qdb_cif target ACCOUNT ONLY, while Housing Loan customers are CONTACTS, so an HL-originated Litigation Request has no column for its customer. DECISION REQUIRED (authorisation section 34). ||| RESTRUCTURING - swept all 3,144 entities and all 1,622 workflows. Four candidates, ALL 0 rows: qdb_customer_restructure_history, qdb_macapplicationrescheduling, qdb_nrgpwriteoff (WCF), qdb_tawarruqaccountrescheduling. ZERO matching workflows. Multiple plausible implementations, none authoritative. DECISION REQUIRED (authorisation section 17). Fallback if none: stop at Strategy -&gt; Restructuring Recommendation -&gt; Assignment -&gt; TAT/Escalation and record the full process as Phase 9. ||| ASSIGNMENT - QDB.RoundRobin v1.0.0.0: Plugins.RoundRobin is ACTIVE on Create of qdb_task (stage 10, sync) and is the ONLY live assignment path; it assigns PROCESS ENGINE TASKS, configured per work item step via qdb_roundrobinmasterdata (2 rows, keyed by qdb_workitemstep). Plugins.UserDeligation and Plugins.ApplicationRoundRobin have NO registered step and never execute. Workflow.ApplyRoundRobin, Workflow.ApplyDelegation and QDB.RoundRobin.AssignApplication are referenced by 0 of 1,523 ACTIVATED workflows (xaml read, nextLink followed - $top suppresses it). No general Smart Assignment service exists for qdb_collectioncase or qdb_collectionactivity. NOT a stop condition: authorisation section 8 already directs isolating an adapter and recording the dependency. KI-09 stands. ||| ESCALATION / TAT - qdb_escalationconiguration 0 rows, qdb_escalations 0 rows, Workflows.CreateEscalationRecord referenced by 0 of 1,523 activated workflows. The stack is WIRED AND DORMANT: nothing live to reuse, nothing live to disturb. DCP already holds the configuration escalation needs - qdb_strategyaction.qdb_escalateifnotcompleted / qdb_escalationhours / qdb_dayoffset and qdb_collectionactivitytype.qdb_slahours - so NO TAT threshold is invented or hard-coded. ||| PROCESS ENGINE - config-rich, execution-zero: qdb_work_item_steps 119 rows, qdb_outcome 166 rows, qdb_request 0, qdb_task 0. Workflows.ApplyProcess referenced by 0 of 1,523 activated workflows. org5869857f is a DESIGN/CONFIG environment. Phase 8 therefore keeps collection work in qdb_collectionactivity (proven end to end in Phases 6-7) and treats the Process Engine as a DOWNSTREAM DESTINATION, not a dependency - routing DCP work through it would mean commissioning the first-ever process execution on this org. ||| THREE GATES applied throughout before calling anything live: does code read it; is that code registered and active; does the branch do something. And the KIND decides the test - a Plugins.* type is dead without a registered step, while a Workflows.* type is a custom workflow ACTIVITY where no step is normal and life is a reference inside a workflow definition. ||| OPEN KI CLASSIFICATION: KI-71 blocker (resolved WP2); KI-09, KI-66, KI-76, KI-96 dependencies; KI-53 non-blocking for build and blocking for a production run; KI-65, KI-72, KI-79, KI-83, KI-95, KI-97 non-blocking. NONE closed by discovery. ||| WORK PACKAGES (hours): WP1 discovery 2.00 COMPLETE; WP2 KI-71 provenance 2.00; WP3 strategy domain model 2.50; WP4 execution + idempotency 3.00; WP5 re-evaluation 3.00; WP6 assignment adapter 2.50; WP7 TAT/escalation 3.00; WP8 Action Plan upgrade 1.50; WP9 Legal hand-off 2.50 HELD; WP10 Legal visibility 2.00 HELD; WP11 Restructuring 1.00 HELD; WP12 operational queues/UI 3.00; WP13 real Dataverse validation 2.00; WP14 Chrome QA journeys 3.00; WP15 regression/hardening 2.00; WP16 docs/ADRs/closure 1.50. ||| DEPENDENCIES: WP2 &lt;- WP1; WP3 &lt;- WP2; WP4 &lt;- WP3; WP5 &lt;- WP4; WP6 &lt;- WP3; WP7 &lt;- WP4; WP8 &lt;- WP2,WP4; WP9/WP10 &lt;- Legal decision; WP11 &lt;- Restructuring decision; WP12 &lt;- WP6,WP7,WP8; WP13/WP15/WP16 &lt;- all; WP14 &lt;- WP12. ||| RISKS: Legal/Restructuring decisions arriving late (WP9-11 isolated, nothing else depends on them); Process Engine later named as the destination for collection work (kept downstream, no DCP work modelled as qdb_task); qdb_origin duplicating a distinction QDB models differently (2 values, optional, cheap to retire); re-evaluation destroying history (explicitly forbidden - completed and manual work is never deleted); assignment adapter becoming a de-facto engine (refuses rather than routes where no capability is configured). ||| RUNTIME GATES PLANNED: strategy evaluation; strategy-generated activity; manual remains distinguishable; duplicate evaluation; re-evaluation after bucket change; assignment; reassignment; TAT; escalation; retry/concurrency; Legal recommendation and hand-off (held); duplicate Legal prevention (held); Legal status visible in the workspace; restructuring (held); large queue paging; rapid filter/search changes; officer-facing error handling; Phase 5/6/7 regression. ||| CALIBRATION CARRIED FORWARD: Phase 7 WP12 was estimated 2.00h and took ~11h27m because the package covered a screen while the work also absorbed a population resolver, deployment, browser QA, cleanup tooling, documentation and an undiscovered platform defect (KI-96). WP12-WP15 here carry the same shape; the deploy -&gt; live validation -&gt; browser QA loop is charged to WP13/WP14 as their own packages. Any revision will record the original figure, the revised figure, the reason and a timestamp - never silently.</v>
       </c>
     </row>
     <row r="11">
